--- a/sources/2B_Manha_1_Bimestre.xlsx
+++ b/sources/2B_Manha_1_Bimestre.xlsx
@@ -190,6 +190,21 @@
     <x:t>90%</x:t>
   </x:si>
   <x:si>
+    <x:t>ADRIELLE JESUS VELOZO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKAYOARA DAFNY CASSIANO ANASTACIO DA SILVA</x:t>
   </x:si>
   <x:si>
@@ -202,15 +217,9 @@
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
     <x:t>26</x:t>
   </x:si>
   <x:si>
@@ -271,9 +280,6 @@
     <x:t>BERNARDO LEITE OLIVEIRA</x:t>
   </x:si>
   <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
     <x:t>BRUNO LEONARDO SANTOS MIRANDA</x:t>
   </x:si>
   <x:si>
@@ -346,6 +352,12 @@
     <x:t>77%</x:t>
   </x:si>
   <x:si>
+    <x:t>GUILHERME HENRIQUE OLIVEIRA AGUIAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUILHERME RIBEIRO DE LIMA</x:t>
   </x:si>
   <x:si>
@@ -391,9 +403,6 @@
     <x:t>HUGO DA SILVA OLIVEIRA</x:t>
   </x:si>
   <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
     <x:t>IZAQUE GONZAGA HERNANDES</x:t>
   </x:si>
   <x:si>
@@ -403,6 +412,9 @@
     <x:t>72%</x:t>
   </x:si>
   <x:si>
+    <x:t>JOÃO VICTOR MACEDO DOS REIS BENEDICTO</x:t>
+  </x:si>
+  <x:si>
     <x:t>JULIA ALMEIDA GUIMARAES</x:t>
   </x:si>
   <x:si>
@@ -436,6 +448,12 @@
     <x:t>KYARA GONCALVES RODRIGUES</x:t>
   </x:si>
   <x:si>
+    <x:t>LEANDRO DE MAGALHAES SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0%</x:t>
+  </x:si>
+  <x:si>
     <x:t>LORENNA BARAUNA VENANCIO DA SILVA</x:t>
   </x:si>
   <x:si>
@@ -494,24 +512,6 @@
   </x:si>
   <x:si>
     <x:t>74%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADRIELLE JESUS VELOZO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME HENRIQUE OLIVEIRA AGUIAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOÃO VICTOR MACEDO DOS REIS BENEDICTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEANDRO DE MAGALHAES SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0%</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -1602,7 +1602,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="12">
         <x:v>2</x:v>
@@ -1620,13 +1620,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I14" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K14" s="12">
         <x:v>2</x:v>
@@ -1635,7 +1635,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N14" s="12" t="s">
         <x:v>48</x:v>
@@ -1644,10 +1644,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P14" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R14" s="12" t="s">
         <x:v>48</x:v>
@@ -1656,10 +1656,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U14" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V14" s="12" t="s">
         <x:v>48</x:v>
@@ -1668,13 +1668,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="X14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA14" s="12">
         <x:v>2</x:v>
@@ -1683,7 +1683,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="s">
         <x:v>48</x:v>
@@ -1695,7 +1695,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
         <x:v>48</x:v>
@@ -1704,22 +1704,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AM14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN14" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
         <x:v>48</x:v>
@@ -1728,10 +1728,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR14" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS14" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
         <x:v>48</x:v>
@@ -1740,33 +1740,33 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY14" s="12">
-        <x:v>132</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AZ14" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA14" s="12">
-        <x:v>94</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="BB14" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:54">
       <x:c r="A15" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C15" s="12">
         <x:v>3</x:v>
@@ -1784,22 +1784,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M15" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N15" s="12" t="s">
         <x:v>48</x:v>
@@ -1808,10 +1808,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P15" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="R15" s="12" t="s">
         <x:v>48</x:v>
@@ -1820,10 +1820,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V15" s="12" t="s">
         <x:v>48</x:v>
@@ -1832,22 +1832,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="X15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="Z15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AA15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="s">
         <x:v>48</x:v>
@@ -1856,10 +1856,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AF15" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AH15" s="12" t="s">
         <x:v>48</x:v>
@@ -1868,22 +1868,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AJ15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK15" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AL15" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AM15" s="12">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP15" s="12" t="s">
         <x:v>48</x:v>
@@ -1892,10 +1892,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
         <x:v>48</x:v>
@@ -1904,22 +1904,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AV15" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AW15" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AX15" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY15" s="12">
-        <x:v>34</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="AZ15" s="12" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="BA15" s="12">
-        <x:v>31</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
         <x:v>71</x:v>
@@ -1930,7 +1930,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C16" s="12">
         <x:v>4</x:v>
@@ -1948,10 +1948,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J16" s="12" t="s">
         <x:v>48</x:v>
@@ -1960,10 +1960,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N16" s="12" t="s">
         <x:v>48</x:v>
@@ -1972,7 +1972,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P16" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="s">
         <x:v>48</x:v>
@@ -1984,10 +1984,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T16" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
         <x:v>48</x:v>
@@ -1996,10 +1996,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="X16" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z16" s="12" t="s">
         <x:v>48</x:v>
@@ -2011,7 +2011,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="s">
         <x:v>48</x:v>
@@ -2020,10 +2020,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF16" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AG16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH16" s="12" t="s">
         <x:v>48</x:v>
@@ -2032,22 +2032,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AJ16" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AK16" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AK16" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="AL16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO16" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AP16" s="12" t="s">
         <x:v>48</x:v>
@@ -2056,7 +2056,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS16" s="12" t="s">
         <x:v>48</x:v>
@@ -2068,7 +2068,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AV16" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AW16" s="12" t="s">
         <x:v>51</x:v>
@@ -2077,24 +2077,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY16" s="12">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AZ16" s="12" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="BA16" s="12">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BB16" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:54">
       <x:c r="A17" s="11" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C17" s="12">
         <x:v>5</x:v>
@@ -2112,10 +2112,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
         <x:v>48</x:v>
@@ -2124,10 +2124,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
         <x:v>48</x:v>
@@ -2136,7 +2136,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P17" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="s">
         <x:v>48</x:v>
@@ -2148,7 +2148,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="T17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U17" s="12" t="s">
         <x:v>48</x:v>
@@ -2160,10 +2160,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="X17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z17" s="12" t="s">
         <x:v>48</x:v>
@@ -2172,10 +2172,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AB17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD17" s="12" t="s">
         <x:v>48</x:v>
@@ -2184,7 +2184,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF17" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG17" s="12" t="s">
         <x:v>48</x:v>
@@ -2208,7 +2208,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AN17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO17" s="12" t="s">
         <x:v>48</x:v>
@@ -2220,10 +2220,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AR17" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS17" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT17" s="12" t="s">
         <x:v>48</x:v>
@@ -2232,33 +2232,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AV17" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW17" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX17" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY17" s="12">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AZ17" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BA17" s="12">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BB17" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:54">
       <x:c r="A18" s="11" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C18" s="12">
         <x:v>6</x:v>
@@ -2276,10 +2276,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J18" s="12" t="s">
         <x:v>48</x:v>
@@ -2288,10 +2288,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
         <x:v>48</x:v>
@@ -2300,10 +2300,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R18" s="12" t="s">
         <x:v>48</x:v>
@@ -2312,10 +2312,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
         <x:v>48</x:v>
@@ -2324,10 +2324,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="X18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
         <x:v>48</x:v>
@@ -2336,10 +2336,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD18" s="12" t="s">
         <x:v>48</x:v>
@@ -2348,10 +2348,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
         <x:v>48</x:v>
@@ -2360,10 +2360,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
         <x:v>48</x:v>
@@ -2372,10 +2372,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
         <x:v>48</x:v>
@@ -2384,7 +2384,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
         <x:v>51</x:v>
@@ -2396,33 +2396,33 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AV18" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY18" s="12">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AZ18" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BA18" s="12">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BB18" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:54">
       <x:c r="A19" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="12">
         <x:v>7</x:v>
@@ -2440,10 +2440,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="H19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J19" s="12" t="s">
         <x:v>48</x:v>
@@ -2452,10 +2452,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="L19" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N19" s="12" t="s">
         <x:v>48</x:v>
@@ -2464,10 +2464,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R19" s="12" t="s">
         <x:v>48</x:v>
@@ -2476,10 +2476,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="T19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V19" s="12" t="s">
         <x:v>48</x:v>
@@ -2488,10 +2488,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="X19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Y19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z19" s="12" t="s">
         <x:v>48</x:v>
@@ -2500,10 +2500,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AB19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="s">
         <x:v>48</x:v>
@@ -2512,10 +2512,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AF19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
         <x:v>48</x:v>
@@ -2524,10 +2524,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AJ19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
         <x:v>48</x:v>
@@ -2536,10 +2536,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AN19" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AO19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP19" s="12" t="s">
         <x:v>48</x:v>
@@ -2548,10 +2548,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
         <x:v>48</x:v>
@@ -2560,7 +2560,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW19" s="12" t="s">
         <x:v>48</x:v>
@@ -2569,24 +2569,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY19" s="12">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="AZ19" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BA19" s="12">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BB19" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:54">
       <x:c r="A20" s="11" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C20" s="12">
         <x:v>8</x:v>
@@ -2604,10 +2604,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
         <x:v>48</x:v>
@@ -2616,7 +2616,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
         <x:v>48</x:v>
@@ -2631,7 +2631,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
         <x:v>48</x:v>
@@ -2640,7 +2640,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
         <x:v>48</x:v>
@@ -2652,19 +2652,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
         <x:v>51</x:v>
@@ -2676,10 +2676,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
         <x:v>48</x:v>
@@ -2688,7 +2688,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
         <x:v>48</x:v>
@@ -2700,10 +2700,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
         <x:v>48</x:v>
@@ -2712,10 +2712,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
         <x:v>48</x:v>
@@ -2724,7 +2724,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW20" s="12" t="s">
         <x:v>48</x:v>
@@ -2733,24 +2733,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY20" s="12">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AZ20" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BA20" s="12">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BB20" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:54">
       <x:c r="A21" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C21" s="12">
         <x:v>9</x:v>
@@ -2768,7 +2768,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
         <x:v>51</x:v>
@@ -2780,7 +2780,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
         <x:v>48</x:v>
@@ -2792,10 +2792,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R21" s="12" t="s">
         <x:v>48</x:v>
@@ -2804,7 +2804,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="T21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
         <x:v>48</x:v>
@@ -2816,19 +2816,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
         <x:v>51</x:v>
@@ -2840,10 +2840,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>48</x:v>
@@ -2852,7 +2852,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AJ21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
         <x:v>48</x:v>
@@ -2864,10 +2864,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
         <x:v>48</x:v>
@@ -2876,10 +2876,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
         <x:v>48</x:v>
@@ -2888,7 +2888,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AV21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW21" s="12" t="s">
         <x:v>48</x:v>
@@ -2897,16 +2897,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY21" s="12">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AZ21" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA21" s="12">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:54">
@@ -2914,7 +2914,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C22" s="12">
         <x:v>10</x:v>
@@ -2932,10 +2932,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
         <x:v>48</x:v>
@@ -2944,10 +2944,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N22" s="12" t="s">
         <x:v>48</x:v>
@@ -2956,7 +2956,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="P22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q22" s="12" t="s">
         <x:v>50</x:v>
@@ -2968,10 +2968,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V22" s="12" t="s">
         <x:v>48</x:v>
@@ -2980,19 +2980,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="X22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Y22" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AB22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
         <x:v>51</x:v>
@@ -3004,10 +3004,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AF22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
         <x:v>48</x:v>
@@ -3016,22 +3016,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM22" s="12">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AO22" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP22" s="12" t="s">
         <x:v>48</x:v>
@@ -3040,10 +3040,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
         <x:v>48</x:v>
@@ -3052,25 +3052,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AV22" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX22" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY22" s="12">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AZ22" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BA22" s="12">
-        <x:v>49</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BB22" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:54">
@@ -3078,7 +3078,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="12">
         <x:v>11</x:v>
@@ -3096,10 +3096,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J23" s="12" t="s">
         <x:v>48</x:v>
@@ -3108,10 +3108,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>48</x:v>
@@ -3120,10 +3120,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="P23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
         <x:v>48</x:v>
@@ -3132,10 +3132,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
         <x:v>48</x:v>
@@ -3144,19 +3144,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
         <x:v>51</x:v>
@@ -3168,10 +3168,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
         <x:v>48</x:v>
@@ -3180,22 +3180,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AP23" s="12" t="s">
         <x:v>48</x:v>
@@ -3207,7 +3207,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
         <x:v>48</x:v>
@@ -3216,7 +3216,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW23" s="12" t="s">
         <x:v>51</x:v>
@@ -3225,24 +3225,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY23" s="12">
-        <x:v>7</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BA23" s="12">
-        <x:v>7</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:54">
       <x:c r="A24" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="12">
         <x:v>12</x:v>
@@ -3260,10 +3260,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
         <x:v>48</x:v>
@@ -3272,10 +3272,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>48</x:v>
@@ -3284,10 +3284,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q24" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R24" s="12" t="s">
         <x:v>48</x:v>
@@ -3296,10 +3296,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
         <x:v>48</x:v>
@@ -3308,10 +3308,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z24" s="12" t="s">
         <x:v>48</x:v>
@@ -3320,10 +3320,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AB24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>48</x:v>
@@ -3332,10 +3332,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
         <x:v>48</x:v>
@@ -3344,10 +3344,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>48</x:v>
@@ -3356,10 +3356,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AN24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
         <x:v>48</x:v>
@@ -3368,10 +3368,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
         <x:v>48</x:v>
@@ -3380,33 +3380,33 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AV24" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY24" s="12">
-        <x:v>146</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AZ24" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BA24" s="12">
-        <x:v>146</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:54">
       <x:c r="A25" s="11" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C25" s="12">
         <x:v>13</x:v>
@@ -3427,7 +3427,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="I25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J25" s="12" t="s">
         <x:v>48</x:v>
@@ -3439,7 +3439,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N25" s="12" t="s">
         <x:v>48</x:v>
@@ -3451,7 +3451,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="Q25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="R25" s="12" t="s">
         <x:v>48</x:v>
@@ -3463,7 +3463,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="V25" s="12" t="s">
         <x:v>48</x:v>
@@ -3475,7 +3475,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="s">
         <x:v>48</x:v>
@@ -3487,7 +3487,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD25" s="12" t="s">
         <x:v>48</x:v>
@@ -3496,10 +3496,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AF25" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="AH25" s="12" t="s">
         <x:v>48</x:v>
@@ -3511,7 +3511,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>48</x:v>
@@ -3523,7 +3523,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AP25" s="12" t="s">
         <x:v>48</x:v>
@@ -3535,7 +3535,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AT25" s="12" t="s">
         <x:v>48</x:v>
@@ -3547,19 +3547,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AW25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AX25" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY25" s="12">
-        <x:v>24</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="AZ25" s="12" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="BA25" s="12">
-        <x:v>24</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="BB25" s="12" t="s">
         <x:v>94</x:v>
@@ -3570,7 +3570,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="12">
         <x:v>14</x:v>
@@ -3591,7 +3591,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
         <x:v>48</x:v>
@@ -3603,7 +3603,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N26" s="12" t="s">
         <x:v>48</x:v>
@@ -3612,7 +3612,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="P26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q26" s="12" t="s">
         <x:v>51</x:v>
@@ -3627,7 +3627,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V26" s="12" t="s">
         <x:v>48</x:v>
@@ -3639,7 +3639,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="s">
         <x:v>48</x:v>
@@ -3663,7 +3663,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
         <x:v>48</x:v>
@@ -3675,7 +3675,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL26" s="12" t="s">
         <x:v>48</x:v>
@@ -3699,7 +3699,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
         <x:v>48</x:v>
@@ -3717,24 +3717,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY26" s="12">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AZ26" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BA26" s="12">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BB26" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:54">
       <x:c r="A27" s="11" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C27" s="12">
         <x:v>15</x:v>
@@ -3752,10 +3752,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
         <x:v>48</x:v>
@@ -3764,7 +3764,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
         <x:v>48</x:v>
@@ -3776,10 +3776,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
         <x:v>48</x:v>
@@ -3788,7 +3788,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
         <x:v>48</x:v>
@@ -3800,7 +3800,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
         <x:v>48</x:v>
@@ -3812,10 +3812,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>48</x:v>
@@ -3824,10 +3824,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
         <x:v>48</x:v>
@@ -3836,10 +3836,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>48</x:v>
@@ -3848,7 +3848,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
         <x:v>51</x:v>
@@ -3860,7 +3860,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
         <x:v>48</x:v>
@@ -3872,7 +3872,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
         <x:v>48</x:v>
@@ -3881,16 +3881,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY27" s="12">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AZ27" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA27" s="12">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:54">
@@ -3898,7 +3898,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="12">
         <x:v>16</x:v>
@@ -3916,10 +3916,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
         <x:v>48</x:v>
@@ -3928,10 +3928,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
         <x:v>48</x:v>
@@ -3940,10 +3940,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="P28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
         <x:v>48</x:v>
@@ -3952,10 +3952,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
         <x:v>48</x:v>
@@ -3964,10 +3964,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
         <x:v>48</x:v>
@@ -3976,10 +3976,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
         <x:v>48</x:v>
@@ -3988,10 +3988,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
         <x:v>48</x:v>
@@ -4000,22 +4000,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
         <x:v>48</x:v>
@@ -4024,10 +4024,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
         <x:v>48</x:v>
@@ -4036,33 +4036,33 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX28" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY28" s="12">
-        <x:v>42</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AZ28" s="12" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="BA28" s="12">
-        <x:v>37</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:54">
       <x:c r="A29" s="11" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="12">
         <x:v>17</x:v>
@@ -4080,22 +4080,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N29" s="12" t="s">
         <x:v>48</x:v>
@@ -4107,7 +4107,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
         <x:v>48</x:v>
@@ -4116,10 +4116,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
         <x:v>48</x:v>
@@ -4128,22 +4128,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>48</x:v>
@@ -4152,10 +4152,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>48</x:v>
@@ -4164,22 +4164,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AM29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
         <x:v>48</x:v>
@@ -4188,10 +4188,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
         <x:v>48</x:v>
@@ -4203,30 +4203,30 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY29" s="12">
-        <x:v>107</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="BA29" s="12">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="BB29" s="12" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="BA29" s="12">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="BB29" s="12" t="s">
-        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:54">
       <x:c r="A30" s="11" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
@@ -4244,22 +4244,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="L30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>48</x:v>
@@ -4268,10 +4268,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
         <x:v>48</x:v>
@@ -4280,10 +4280,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
         <x:v>48</x:v>
@@ -4292,22 +4292,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Z30" s="12" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="Z30" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="AA30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>48</x:v>
@@ -4316,10 +4316,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
         <x:v>48</x:v>
@@ -4328,22 +4328,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
         <x:v>48</x:v>
@@ -4352,10 +4352,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
         <x:v>48</x:v>
@@ -4364,25 +4364,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY30" s="12">
-        <x:v>60</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="BA30" s="12">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="BB30" s="12" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="BA30" s="12">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="BB30" s="12" t="s">
-        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:54">
@@ -4390,7 +4390,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C31" s="12">
         <x:v>19</x:v>
@@ -4408,19 +4408,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
         <x:v>51</x:v>
@@ -4432,10 +4432,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
         <x:v>48</x:v>
@@ -4444,10 +4444,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
         <x:v>48</x:v>
@@ -4456,22 +4456,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AA31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
         <x:v>48</x:v>
@@ -4480,10 +4480,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
         <x:v>48</x:v>
@@ -4492,22 +4492,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AM31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
         <x:v>48</x:v>
@@ -4516,10 +4516,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
         <x:v>48</x:v>
@@ -4528,33 +4528,33 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AX31" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AY31" s="12">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="AX31" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AY31" s="12">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BA31" s="12">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:54">
       <x:c r="A32" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C32" s="12">
         <x:v>20</x:v>
@@ -4572,10 +4572,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
         <x:v>48</x:v>
@@ -4584,10 +4584,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>48</x:v>
@@ -4599,7 +4599,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
         <x:v>48</x:v>
@@ -4608,10 +4608,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
         <x:v>48</x:v>
@@ -4620,10 +4620,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
         <x:v>48</x:v>
@@ -4632,10 +4632,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
         <x:v>48</x:v>
@@ -4644,10 +4644,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>48</x:v>
@@ -4656,22 +4656,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
         <x:v>48</x:v>
@@ -4680,7 +4680,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
         <x:v>48</x:v>
@@ -4692,33 +4692,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX32" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY32" s="12">
-        <x:v>43</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA32" s="12">
-        <x:v>38</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB32" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:54">
       <x:c r="A33" s="11" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="12">
         <x:v>21</x:v>
@@ -4736,22 +4736,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
         <x:v>48</x:v>
@@ -4760,10 +4760,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
         <x:v>48</x:v>
@@ -4772,10 +4772,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
         <x:v>48</x:v>
@@ -4784,10 +4784,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>63</x:v>
@@ -4796,10 +4796,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
         <x:v>48</x:v>
@@ -4808,10 +4808,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>48</x:v>
@@ -4820,22 +4820,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AM33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP33" s="12" t="s">
         <x:v>48</x:v>
@@ -4844,10 +4844,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
         <x:v>48</x:v>
@@ -4856,33 +4856,33 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY33" s="12">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AZ33" s="12" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="AZ33" s="12" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="BA33" s="12">
-        <x:v>84</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:54">
       <x:c r="A34" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="12">
         <x:v>22</x:v>
@@ -4900,10 +4900,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>48</x:v>
@@ -4912,10 +4912,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>48</x:v>
@@ -4924,10 +4924,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
         <x:v>48</x:v>
@@ -4936,10 +4936,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
         <x:v>48</x:v>
@@ -4948,10 +4948,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>48</x:v>
@@ -4960,10 +4960,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>48</x:v>
@@ -4972,10 +4972,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>48</x:v>
@@ -4984,22 +4984,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AM34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>107</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
         <x:v>48</x:v>
@@ -5008,10 +5008,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
         <x:v>48</x:v>
@@ -5020,33 +5020,33 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY34" s="12">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BA34" s="12">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:54">
       <x:c r="A35" s="11" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C35" s="12">
         <x:v>23</x:v>
@@ -5064,22 +5064,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
         <x:v>48</x:v>
@@ -5088,10 +5088,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
         <x:v>48</x:v>
@@ -5100,10 +5100,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="T35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
         <x:v>48</x:v>
@@ -5112,22 +5112,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="Z35" s="12" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="Z35" s="12" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="AA35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>48</x:v>
@@ -5136,10 +5136,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AF35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>48</x:v>
@@ -5148,22 +5148,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AM35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AN35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
         <x:v>48</x:v>
@@ -5172,10 +5172,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
         <x:v>48</x:v>
@@ -5184,25 +5184,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY35" s="12">
-        <x:v>65</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AZ35" s="12" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="BA35" s="12">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="BB35" s="12" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="BA35" s="12">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="BB35" s="12" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:54">
@@ -5210,7 +5210,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C36" s="12">
         <x:v>24</x:v>
@@ -5228,10 +5228,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
         <x:v>48</x:v>
@@ -5240,7 +5240,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
         <x:v>48</x:v>
@@ -5252,10 +5252,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R36" s="12" t="s">
         <x:v>48</x:v>
@@ -5264,10 +5264,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
         <x:v>48</x:v>
@@ -5276,10 +5276,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
         <x:v>48</x:v>
@@ -5288,10 +5288,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>48</x:v>
@@ -5300,10 +5300,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>48</x:v>
@@ -5312,22 +5312,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AM36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>48</x:v>
@@ -5336,10 +5336,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
         <x:v>48</x:v>
@@ -5348,22 +5348,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY36" s="12">
-        <x:v>0</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AZ36" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BA36" s="12">
-        <x:v>0</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BB36" s="12" t="s">
         <x:v>121</x:v>
@@ -5374,7 +5374,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C37" s="12">
         <x:v>25</x:v>
@@ -5392,22 +5392,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
         <x:v>48</x:v>
@@ -5416,10 +5416,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
         <x:v>48</x:v>
@@ -5428,7 +5428,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
         <x:v>52</x:v>
@@ -5440,22 +5440,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AA37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>48</x:v>
@@ -5464,10 +5464,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>48</x:v>
@@ -5476,22 +5476,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AM37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
         <x:v>48</x:v>
@@ -5500,10 +5500,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
         <x:v>48</x:v>
@@ -5512,33 +5512,33 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX37" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY37" s="12">
-        <x:v>96</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="BA37" s="12">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:54">
       <x:c r="A38" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
@@ -5556,10 +5556,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>48</x:v>
@@ -5568,7 +5568,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
         <x:v>48</x:v>
@@ -5580,10 +5580,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
         <x:v>48</x:v>
@@ -5592,10 +5592,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
         <x:v>48</x:v>
@@ -5604,10 +5604,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
         <x:v>48</x:v>
@@ -5616,7 +5616,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
         <x:v>48</x:v>
@@ -5628,7 +5628,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
         <x:v>48</x:v>
@@ -5640,7 +5640,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
         <x:v>48</x:v>
@@ -5652,10 +5652,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
         <x:v>48</x:v>
@@ -5664,10 +5664,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>48</x:v>
@@ -5676,7 +5676,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
         <x:v>48</x:v>
@@ -5685,24 +5685,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY38" s="12">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ38" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA38" s="12">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:54">
       <x:c r="A39" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C39" s="12">
         <x:v>27</x:v>
@@ -5720,22 +5720,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>48</x:v>
@@ -5744,7 +5744,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
         <x:v>50</x:v>
@@ -5756,10 +5756,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
         <x:v>48</x:v>
@@ -5768,22 +5768,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AA39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>48</x:v>
@@ -5792,10 +5792,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>48</x:v>
@@ -5804,22 +5804,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AM39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
         <x:v>48</x:v>
@@ -5828,10 +5828,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>48</x:v>
@@ -5840,22 +5840,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY39" s="12">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BA39" s="12">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>127</x:v>
@@ -5866,7 +5866,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C40" s="12">
         <x:v>28</x:v>
@@ -5884,10 +5884,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
         <x:v>48</x:v>
@@ -5896,10 +5896,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>48</x:v>
@@ -5908,10 +5908,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
         <x:v>48</x:v>
@@ -5923,7 +5923,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>48</x:v>
@@ -5932,10 +5932,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="X40" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>48</x:v>
@@ -5944,7 +5944,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
         <x:v>48</x:v>
@@ -5956,10 +5956,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AF40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>48</x:v>
@@ -5968,22 +5968,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
         <x:v>48</x:v>
@@ -5992,10 +5992,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
         <x:v>48</x:v>
@@ -6004,7 +6004,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AV40" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
         <x:v>48</x:v>
@@ -6013,16 +6013,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY40" s="12">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA40" s="12">
-        <x:v>26</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:54">
@@ -6030,7 +6030,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C41" s="12">
         <x:v>29</x:v>
@@ -6048,19 +6048,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
         <x:v>48</x:v>
@@ -6072,10 +6072,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="P41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
         <x:v>48</x:v>
@@ -6084,7 +6084,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
         <x:v>51</x:v>
@@ -6096,10 +6096,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>48</x:v>
@@ -6108,10 +6108,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>48</x:v>
@@ -6120,10 +6120,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>48</x:v>
@@ -6132,22 +6132,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="AN41" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>48</x:v>
@@ -6156,10 +6156,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>48</x:v>
@@ -6168,25 +6168,25 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY41" s="12">
-        <x:v>48</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AZ41" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA41" s="12">
-        <x:v>45</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:54">
@@ -6194,7 +6194,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
@@ -6212,7 +6212,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
         <x:v>63</x:v>
@@ -6224,10 +6224,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>48</x:v>
@@ -6236,10 +6236,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
         <x:v>48</x:v>
@@ -6248,10 +6248,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
         <x:v>48</x:v>
@@ -6263,7 +6263,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>48</x:v>
@@ -6275,7 +6275,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>48</x:v>
@@ -6284,10 +6284,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
         <x:v>48</x:v>
@@ -6296,10 +6296,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>48</x:v>
@@ -6311,7 +6311,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
         <x:v>48</x:v>
@@ -6320,10 +6320,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>48</x:v>
@@ -6332,7 +6332,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
         <x:v>50</x:v>
@@ -6341,24 +6341,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY42" s="12">
-        <x:v>110</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="BA42" s="12">
-        <x:v>110</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:54">
       <x:c r="A43" s="11" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
@@ -6376,10 +6376,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
         <x:v>48</x:v>
@@ -6388,10 +6388,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
         <x:v>48</x:v>
@@ -6400,10 +6400,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
         <x:v>48</x:v>
@@ -6412,10 +6412,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
         <x:v>48</x:v>
@@ -6424,10 +6424,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
         <x:v>48</x:v>
@@ -6436,7 +6436,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
         <x:v>48</x:v>
@@ -6448,10 +6448,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
         <x:v>48</x:v>
@@ -6460,19 +6460,19 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
         <x:v>50</x:v>
@@ -6484,10 +6484,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
         <x:v>48</x:v>
@@ -6496,7 +6496,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
         <x:v>48</x:v>
@@ -6505,24 +6505,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY43" s="12">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA43" s="12">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:54">
       <x:c r="A44" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
@@ -6540,13 +6540,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>32</x:v>
@@ -6564,10 +6564,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
         <x:v>48</x:v>
@@ -6576,10 +6576,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
         <x:v>48</x:v>
@@ -6588,10 +6588,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
         <x:v>48</x:v>
@@ -6600,10 +6600,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>48</x:v>
@@ -6612,10 +6612,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>48</x:v>
@@ -6627,10 +6627,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM44" s="12">
         <x:v>32</x:v>
@@ -6639,7 +6639,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
         <x:v>48</x:v>
@@ -6648,10 +6648,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>48</x:v>
@@ -6660,33 +6660,33 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY44" s="12">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BA44" s="12">
-        <x:v>12</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:54">
       <x:c r="A45" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C45" s="12">
         <x:v>33</x:v>
@@ -6704,10 +6704,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
         <x:v>48</x:v>
@@ -6716,10 +6716,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>48</x:v>
@@ -6728,10 +6728,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
         <x:v>48</x:v>
@@ -6740,10 +6740,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
         <x:v>48</x:v>
@@ -6752,10 +6752,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
         <x:v>48</x:v>
@@ -6764,10 +6764,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>48</x:v>
@@ -6776,10 +6776,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
         <x:v>48</x:v>
@@ -6791,7 +6791,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>48</x:v>
@@ -6800,10 +6800,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AO45" s="12" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="AO45" s="12" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
         <x:v>48</x:v>
@@ -6812,10 +6812,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
         <x:v>48</x:v>
@@ -6824,7 +6824,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
         <x:v>50</x:v>
@@ -6833,16 +6833,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY45" s="12">
-        <x:v>32</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="BA45" s="12">
-        <x:v>32</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:54">
@@ -6850,7 +6850,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C46" s="12">
         <x:v>34</x:v>
@@ -6868,10 +6868,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>48</x:v>
@@ -6880,10 +6880,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>48</x:v>
@@ -6904,7 +6904,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
         <x:v>48</x:v>
@@ -6916,10 +6916,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
         <x:v>48</x:v>
@@ -6928,10 +6928,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>48</x:v>
@@ -6940,10 +6940,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
         <x:v>48</x:v>
@@ -6952,7 +6952,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
         <x:v>48</x:v>
@@ -6964,10 +6964,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
         <x:v>48</x:v>
@@ -6976,10 +6976,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
         <x:v>48</x:v>
@@ -6988,33 +6988,33 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX46" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY46" s="12">
-        <x:v>28</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="BA46" s="12">
-        <x:v>28</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:54">
       <x:c r="A47" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C47" s="12">
         <x:v>35</x:v>
@@ -7032,10 +7032,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J47" s="12" t="s">
         <x:v>48</x:v>
@@ -7044,10 +7044,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>48</x:v>
@@ -7056,7 +7056,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
         <x:v>48</x:v>
@@ -7068,10 +7068,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
         <x:v>48</x:v>
@@ -7080,10 +7080,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>48</x:v>
@@ -7092,7 +7092,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
         <x:v>48</x:v>
@@ -7104,10 +7104,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>48</x:v>
@@ -7119,16 +7119,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AM47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
         <x:v>48</x:v>
@@ -7140,10 +7140,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
         <x:v>48</x:v>
@@ -7152,7 +7152,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
         <x:v>48</x:v>
@@ -7161,24 +7161,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY47" s="12">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="BA47" s="12">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:54">
       <x:c r="A48" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
@@ -7196,153 +7196,153 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AA48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AE48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AI48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AM48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AQ48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AU48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AY48" s="12">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BA48" s="12">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:54">
       <x:c r="A49" s="11" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C49" s="12">
         <x:v>37</x:v>
@@ -7360,22 +7360,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="L49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>48</x:v>
@@ -7384,10 +7384,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
         <x:v>48</x:v>
@@ -7396,10 +7396,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
         <x:v>48</x:v>
@@ -7408,10 +7408,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>48</x:v>
@@ -7420,10 +7420,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>48</x:v>
@@ -7432,10 +7432,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>48</x:v>
@@ -7447,19 +7447,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="AO49" s="12" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="AO49" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
         <x:v>48</x:v>
@@ -7468,10 +7468,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
         <x:v>48</x:v>
@@ -7480,33 +7480,33 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY49" s="12">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BA49" s="12">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:54">
       <x:c r="A50" s="11" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
@@ -7524,10 +7524,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H50" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>48</x:v>
@@ -7536,10 +7536,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>48</x:v>
@@ -7548,10 +7548,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="P50" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
         <x:v>48</x:v>
@@ -7563,7 +7563,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
         <x:v>48</x:v>
@@ -7572,10 +7572,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="X50" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z50" s="12" t="s">
         <x:v>48</x:v>
@@ -7584,7 +7584,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>50</x:v>
@@ -7596,10 +7596,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>48</x:v>
@@ -7608,22 +7608,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
         <x:v>48</x:v>
@@ -7632,7 +7632,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
         <x:v>51</x:v>
@@ -7647,30 +7647,30 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY50" s="12">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BA50" s="12">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:54">
       <x:c r="A51" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C51" s="12">
         <x:v>39</x:v>
@@ -7688,10 +7688,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>48</x:v>
@@ -7712,10 +7712,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
         <x:v>48</x:v>
@@ -7724,10 +7724,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
         <x:v>48</x:v>
@@ -7736,10 +7736,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
         <x:v>48</x:v>
@@ -7748,7 +7748,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
         <x:v>48</x:v>
@@ -7760,7 +7760,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AF51" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
         <x:v>48</x:v>
@@ -7772,19 +7772,19 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AM51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
         <x:v>48</x:v>
@@ -7796,10 +7796,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
         <x:v>48</x:v>
@@ -7817,24 +7817,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY51" s="12">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BA51" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:54">
       <x:c r="A52" s="11" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
@@ -7852,10 +7852,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
         <x:v>48</x:v>
@@ -7864,10 +7864,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N52" s="12" t="s">
         <x:v>48</x:v>
@@ -7876,7 +7876,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
         <x:v>48</x:v>
@@ -7888,7 +7888,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
         <x:v>48</x:v>
@@ -7900,10 +7900,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z52" s="12" t="s">
         <x:v>48</x:v>
@@ -7912,10 +7912,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>48</x:v>
@@ -7924,10 +7924,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>48</x:v>
@@ -7936,22 +7936,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
         <x:v>48</x:v>
@@ -7960,10 +7960,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
         <x:v>48</x:v>
@@ -7972,7 +7972,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AV52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
         <x:v>51</x:v>
@@ -7981,24 +7981,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY52" s="12">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AZ52" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA52" s="12">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:54">
       <x:c r="A53" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C53" s="12">
         <x:v>41</x:v>
@@ -8016,22 +8016,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N53" s="12" t="s">
         <x:v>48</x:v>
@@ -8040,7 +8040,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
         <x:v>48</x:v>
@@ -8052,7 +8052,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
         <x:v>48</x:v>
@@ -8064,10 +8064,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z53" s="12" t="s">
         <x:v>48</x:v>
@@ -8076,10 +8076,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>48</x:v>
@@ -8088,10 +8088,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>48</x:v>
@@ -8100,22 +8100,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AK53" s="12" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AK53" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="AL53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="AN53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
         <x:v>48</x:v>
@@ -8124,10 +8124,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
         <x:v>48</x:v>
@@ -8136,33 +8136,33 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX53" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY53" s="12">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BA53" s="12">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:54">
       <x:c r="A54" s="11" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C54" s="12">
         <x:v>42</x:v>
@@ -8180,10 +8180,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
         <x:v>48</x:v>
@@ -8192,10 +8192,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>48</x:v>
@@ -8204,10 +8204,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R54" s="12" t="s">
         <x:v>48</x:v>
@@ -8216,7 +8216,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
         <x:v>51</x:v>
@@ -8228,10 +8228,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
         <x:v>48</x:v>
@@ -8240,10 +8240,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>48</x:v>
@@ -8252,10 +8252,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>48</x:v>
@@ -8264,22 +8264,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AM54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
         <x:v>48</x:v>
@@ -8288,10 +8288,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
         <x:v>48</x:v>
@@ -8300,33 +8300,33 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AX54" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY54" s="12">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BA54" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:54">
       <x:c r="A55" s="11" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C55" s="12">
         <x:v>43</x:v>
@@ -8344,7 +8344,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
         <x:v>48</x:v>
@@ -8356,10 +8356,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>48</x:v>
@@ -8368,10 +8368,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R55" s="12" t="s">
         <x:v>48</x:v>
@@ -8380,10 +8380,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
         <x:v>48</x:v>
@@ -8392,10 +8392,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z55" s="12" t="s">
         <x:v>48</x:v>
@@ -8404,7 +8404,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
         <x:v>48</x:v>
@@ -8416,10 +8416,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>48</x:v>
@@ -8428,22 +8428,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
         <x:v>48</x:v>
@@ -8452,7 +8452,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
         <x:v>48</x:v>
@@ -8464,7 +8464,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
         <x:v>48</x:v>
@@ -8473,24 +8473,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY55" s="12">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BA55" s="12">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:54">
       <x:c r="A56" s="11" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C56" s="12">
         <x:v>44</x:v>
@@ -8508,10 +8508,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
         <x:v>48</x:v>
@@ -8520,10 +8520,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>48</x:v>
@@ -8532,10 +8532,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="P56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
         <x:v>48</x:v>
@@ -8544,10 +8544,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V56" s="12" t="s">
         <x:v>48</x:v>
@@ -8556,10 +8556,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>48</x:v>
@@ -8568,7 +8568,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
         <x:v>51</x:v>
@@ -8580,10 +8580,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>48</x:v>
@@ -8592,22 +8592,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
         <x:v>48</x:v>
@@ -8616,10 +8616,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
         <x:v>48</x:v>
@@ -8628,7 +8628,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
         <x:v>51</x:v>
@@ -8637,24 +8637,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY56" s="12">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BA56" s="12">
-        <x:v>47</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:54">
       <x:c r="A57" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C57" s="12">
         <x:v>45</x:v>
@@ -8672,10 +8672,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J57" s="12" t="s">
         <x:v>48</x:v>
@@ -8684,10 +8684,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>48</x:v>
@@ -8696,10 +8696,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="P57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R57" s="12" t="s">
         <x:v>48</x:v>
@@ -8708,10 +8708,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V57" s="12" t="s">
         <x:v>48</x:v>
@@ -8720,10 +8720,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z57" s="12" t="s">
         <x:v>48</x:v>
@@ -8732,10 +8732,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>48</x:v>
@@ -8744,10 +8744,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>48</x:v>
@@ -8756,13 +8756,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM57" s="12">
         <x:v>45</x:v>
@@ -8771,7 +8771,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
         <x:v>48</x:v>
@@ -8780,10 +8780,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
         <x:v>48</x:v>
@@ -8792,33 +8792,33 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX57" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY57" s="12">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BA57" s="12">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:54">
       <x:c r="A58" s="11" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C58" s="12">
         <x:v>46</x:v>
@@ -8836,7 +8836,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
         <x:v>47</x:v>
@@ -8848,7 +8848,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="L58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M58" s="12" t="s">
         <x:v>51</x:v>
@@ -8860,10 +8860,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="P58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R58" s="12" t="s">
         <x:v>48</x:v>
@@ -8872,10 +8872,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="T58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V58" s="12" t="s">
         <x:v>48</x:v>
@@ -8884,10 +8884,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z58" s="12" t="s">
         <x:v>48</x:v>
@@ -8896,10 +8896,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AB58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="s">
         <x:v>48</x:v>
@@ -8908,10 +8908,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AF58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH58" s="12" t="s">
         <x:v>48</x:v>
@@ -8920,22 +8920,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AJ58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
         <x:v>48</x:v>
@@ -8944,10 +8944,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
         <x:v>48</x:v>
@@ -8956,10 +8956,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX58" s="12" t="s">
         <x:v>48</x:v>
@@ -8968,21 +8968,21 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BA58" s="12">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:54">
       <x:c r="A59" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C59" s="12">
         <x:v>47</x:v>
@@ -9000,7 +9000,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H59" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
         <x:v>48</x:v>
@@ -9012,10 +9012,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
         <x:v>48</x:v>
@@ -9024,7 +9024,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="P59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
         <x:v>48</x:v>
@@ -9036,7 +9036,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
         <x:v>48</x:v>
@@ -9048,10 +9048,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="X59" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>48</x:v>
@@ -9060,10 +9060,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AB59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>48</x:v>
@@ -9072,34 +9072,34 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AF59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AI59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AM59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="AN59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
         <x:v>48</x:v>
@@ -9108,7 +9108,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
         <x:v>48</x:v>
@@ -9120,7 +9120,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AV59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
         <x:v>48</x:v>
@@ -9129,24 +9129,24 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY59" s="12">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="AZ59" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA59" s="12">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:54">
       <x:c r="A60" s="11" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C60" s="12">
         <x:v>48</x:v>
@@ -9164,7 +9164,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I60" s="12" t="s">
         <x:v>50</x:v>
@@ -9176,7 +9176,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="L60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M60" s="12" t="s">
         <x:v>51</x:v>
@@ -9188,10 +9188,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="P60" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Q60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R60" s="12" t="s">
         <x:v>48</x:v>
@@ -9200,10 +9200,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="T60" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="U60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V60" s="12" t="s">
         <x:v>48</x:v>
@@ -9212,10 +9212,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Y60" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z60" s="12" t="s">
         <x:v>48</x:v>
@@ -9224,7 +9224,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AB60" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC60" s="12" t="s">
         <x:v>51</x:v>
@@ -9236,81 +9236,81 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AF60" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AG60" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AH60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AI60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AJ60" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AK60" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AL60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AM60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AN60" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AO60" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AP60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AQ60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AR60" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AS60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AT60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AU60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AV60" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AW60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AX60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AY60" s="12">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AH60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AI60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AJ60" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AK60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AL60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AM60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AN60" s="12" t="s">
+      <x:c r="AZ60" s="12" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="BA60" s="12">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AO60" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AP60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AQ60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AR60" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AS60" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AT60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AU60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AV60" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AW60" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="AX60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AY60" s="12">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="AZ60" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="BA60" s="12">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="BB60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:54">
       <x:c r="A61" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C61" s="12">
         <x:v>49</x:v>
@@ -9328,22 +9328,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H61" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="L61" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M61" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N61" s="12" t="s">
         <x:v>48</x:v>
@@ -9352,10 +9352,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="P61" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R61" s="12" t="s">
         <x:v>48</x:v>
@@ -9364,10 +9364,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="T61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U61" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V61" s="12" t="s">
         <x:v>48</x:v>
@@ -9376,22 +9376,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="X61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y61" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Z61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AB61" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD61" s="12" t="s">
         <x:v>48</x:v>
@@ -9400,10 +9400,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AF61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG61" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AH61" s="12" t="s">
         <x:v>48</x:v>
@@ -9412,22 +9412,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AJ61" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL61" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AM61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AN61" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO61" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AP61" s="12" t="s">
         <x:v>48</x:v>
@@ -9436,10 +9436,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AR61" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
         <x:v>48</x:v>
@@ -9448,25 +9448,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX61" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY61" s="12">
-        <x:v>81</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="BA61" s="12">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB61" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:54">
@@ -9474,7 +9474,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C62" s="12">
         <x:v>50</x:v>
@@ -9492,10 +9492,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H62" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
         <x:v>48</x:v>
@@ -9504,10 +9504,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
         <x:v>48</x:v>
@@ -9516,10 +9516,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="P62" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q62" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R62" s="12" t="s">
         <x:v>48</x:v>
@@ -9528,10 +9528,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V62" s="12" t="s">
         <x:v>48</x:v>
@@ -9540,10 +9540,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z62" s="12" t="s">
         <x:v>48</x:v>
@@ -9552,10 +9552,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
         <x:v>48</x:v>
@@ -9564,10 +9564,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
         <x:v>48</x:v>
@@ -9576,22 +9576,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AM62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
         <x:v>48</x:v>
@@ -9600,7 +9600,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
         <x:v>51</x:v>
@@ -9612,197 +9612,197 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY62" s="12">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BA62" s="12">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:54">
       <x:c r="A63" s="11" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D63" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E63" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F63" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H63" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L63" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M63" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="O63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="P63" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="Q63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="R63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="S63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="T63" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="U63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="V63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="W63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="X63" s="12" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="Y63" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Z63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AA63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AB63" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AC63" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AD63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AE63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AF63" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AG63" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AH63" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AI63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AJ63" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AK63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AL63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AM63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AN63" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AO63" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AP63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AQ63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AR63" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D63" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E63" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F63" s="12" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H63" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="L63" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="N63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="O63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="P63" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="Q63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="R63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="S63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="T63" s="12" t="s">
+      <x:c r="AS63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AT63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AU63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AV63" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AW63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AX63" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AY63" s="12">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AZ63" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="U63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="V63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="W63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="X63" s="12" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="Y63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Z63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AA63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AB63" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="AC63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AD63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AE63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AF63" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AG63" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AH63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AI63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AJ63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AK63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AL63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AM63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AN63" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="AO63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AP63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AQ63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AR63" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AS63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AT63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AU63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AV63" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="AW63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AX63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AY63" s="12">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ63" s="12" t="s">
-        <x:v>121</x:v>
-      </x:c>
       <x:c r="BA63" s="12">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BB63" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:54">
       <x:c r="A64" s="11" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C64" s="12">
         <x:v>52</x:v>
@@ -9820,10 +9820,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J64" s="12" t="s">
         <x:v>48</x:v>
@@ -9832,10 +9832,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="L64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N64" s="12" t="s">
         <x:v>48</x:v>
@@ -9844,7 +9844,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P64" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="Q64" s="12" t="s">
         <x:v>48</x:v>
@@ -9856,7 +9856,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="T64" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="U64" s="12" t="s">
         <x:v>48</x:v>
@@ -9868,10 +9868,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="X64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Z64" s="12" t="s">
         <x:v>48</x:v>
@@ -9880,10 +9880,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AB64" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AC64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD64" s="12" t="s">
         <x:v>48</x:v>
@@ -9892,10 +9892,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AF64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AH64" s="12" t="s">
         <x:v>48</x:v>
@@ -9904,7 +9904,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AJ64" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK64" s="12" t="s">
         <x:v>48</x:v>
@@ -9916,10 +9916,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AN64" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AO64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP64" s="12" t="s">
         <x:v>48</x:v>
@@ -9928,10 +9928,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AR64" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AS64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT64" s="12" t="s">
         <x:v>48</x:v>
@@ -9940,33 +9940,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AV64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AX64" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AY64" s="12">
-        <x:v>1</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AZ64" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA64" s="12">
-        <x:v>1</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BB64" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:54">
       <x:c r="A65" s="11" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C65" s="12">
         <x:v>53</x:v>
@@ -9984,142 +9984,142 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="L65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="N65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="O65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="P65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="R65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="T65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="V65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="X65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="Z65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AA65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AB65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AE65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AF65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AG65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AI65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AJ65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AM65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AN65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AP65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AQ65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AR65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AS65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AT65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AU65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AV65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AX65" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AY65" s="12">
-        <x:v>0</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AZ65" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="BA65" s="12">
-        <x:v>0</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="BB65" s="12" t="s">
         <x:v>161</x:v>
